--- a/Planejamento/Aquabox_Pinagem_ESP32S3.xlsx
+++ b/Planejamento/Aquabox_Pinagem_ESP32S3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorio_Git\Aquabox_Final\Planejamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E171652-0F61-4F44-B315-71B7AE308E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D44BE2-D6DB-4464-A50C-F4E27139591D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="99">
   <si>
     <t>GPIO</t>
   </si>
@@ -319,13 +319,16 @@
   </si>
   <si>
     <t>Input only / strap</t>
+  </si>
+  <si>
+    <t>PINAGEM DO PROJETO) AQUABOX FINAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,16 +341,41 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -355,13 +383,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -664,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -675,537 +723,555 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D20" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D30" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D32" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C34" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D35" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D36" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C37" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D38" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B39" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D39" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" s="3" t="s">
         <v>97</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Planejamento/Aquabox_Pinagem_ESP32S3.xlsx
+++ b/Planejamento/Aquabox_Pinagem_ESP32S3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorio_Git\Aquabox_Final\Planejamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D44BE2-D6DB-4464-A50C-F4E27139591D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7FC0F3-A6A9-44D6-BB4C-FBDC0F9C2F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinagem Aquabox" sheetId="1" r:id="rId1"/>
@@ -69,15 +69,9 @@
     <t>Botão ENTER</t>
   </si>
   <si>
-    <t>GPIO7</t>
-  </si>
-  <si>
     <t>TFT_BL</t>
   </si>
   <si>
-    <t>PWM Backlight Display</t>
-  </si>
-  <si>
     <t>GPIO8</t>
   </si>
   <si>
@@ -322,6 +316,12 @@
   </si>
   <si>
     <t>PINAGEM DO PROJETO) AQUABOX FINAL</t>
+  </si>
+  <si>
+    <t>Backlight Display</t>
+  </si>
+  <si>
+    <t>3,3V</t>
   </si>
 </sst>
 </file>
@@ -404,12 +404,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,549 +722,549 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="4" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="C17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="4" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="C20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="C22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="3" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="C23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="C24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="C25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="C26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="C27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="C29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="3" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="C31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="C32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="B33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="B34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="B36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="B37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="B38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="C39" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="C40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
